--- a/Collections/EURO/Germany/#EURO#Germany#Regular#[2002-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Germany/#EURO#Germany#Regular#[2002-present]#circulation_quality.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Germany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B32553-5D59-4A4C-8E63-5DE694E3247E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B8BC26-F9F8-4666-B319-E32868E9AD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3563,1623 +3563,7 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="205">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="193">
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -5188,6 +3572,1526 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5220,9 +5124,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="204"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="203" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="202"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -6684,7 +6588,7 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="J3:J20 K3:M3 N3:N20">
-    <cfRule type="containsText" dxfId="201" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="192" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="76">
@@ -6699,7 +6603,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K6 K8:K20">
-    <cfRule type="containsText" dxfId="200" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="191" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="72">
@@ -6714,7 +6618,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="containsText" dxfId="199" priority="69" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="190" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="70">
@@ -6729,7 +6633,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="containsText" dxfId="198" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="189" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="68">
@@ -6744,7 +6648,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L8:L20">
-    <cfRule type="containsText" dxfId="197" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="188" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L8))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="66">
@@ -6759,7 +6663,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L6">
-    <cfRule type="containsText" dxfId="196" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="187" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="64">
@@ -6774,7 +6678,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4">
-    <cfRule type="containsText" dxfId="195" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="186" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="62">
@@ -6789,7 +6693,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7">
-    <cfRule type="containsText" dxfId="194" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="185" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="60">
@@ -6804,7 +6708,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:M20">
-    <cfRule type="containsText" dxfId="193" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="184" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M8))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="58">
@@ -6819,7 +6723,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M6">
-    <cfRule type="containsText" dxfId="192" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="183" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="56">
@@ -6834,7 +6738,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
-    <cfRule type="containsText" dxfId="191" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="182" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="54">
@@ -6849,7 +6753,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7">
-    <cfRule type="containsText" dxfId="190" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="181" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="52">
@@ -6864,7 +6768,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N21:N22 J21:J22 J24 N24">
-    <cfRule type="containsText" dxfId="189" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="180" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="48">
@@ -6879,7 +6783,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:K22 K24">
-    <cfRule type="containsText" dxfId="188" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="179" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="46">
@@ -6894,7 +6798,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L21:L22 L24">
-    <cfRule type="containsText" dxfId="187" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="178" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="44">
@@ -6909,7 +6813,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M21:M22 M24">
-    <cfRule type="containsText" dxfId="186" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="177" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="42">
@@ -6923,8 +6827,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N23 J23">
-    <cfRule type="containsText" dxfId="185" priority="39" operator="containsText" text="*-">
+  <conditionalFormatting sqref="J23 N23">
+    <cfRule type="containsText" dxfId="176" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="40">
@@ -6939,7 +6843,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23">
-    <cfRule type="containsText" dxfId="184" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="175" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="38">
@@ -6954,7 +6858,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23">
-    <cfRule type="containsText" dxfId="183" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="174" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="36">
@@ -6969,7 +6873,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23">
-    <cfRule type="containsText" dxfId="182" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="173" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="34">
@@ -6983,8 +6887,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J25 N25">
-    <cfRule type="containsText" dxfId="181" priority="31" operator="containsText" text="*-">
+  <conditionalFormatting sqref="N25 J25">
+    <cfRule type="containsText" dxfId="172" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="32">
@@ -6999,7 +6903,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="containsText" dxfId="180" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="171" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="30">
@@ -7014,7 +6918,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L25">
-    <cfRule type="containsText" dxfId="179" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="170" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
@@ -7029,7 +6933,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25">
-    <cfRule type="containsText" dxfId="178" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="169" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="26">
@@ -7043,8 +6947,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J26 N26">
-    <cfRule type="containsText" dxfId="177" priority="7" operator="containsText" text="*-">
+  <conditionalFormatting sqref="N26 J26">
+    <cfRule type="containsText" dxfId="168" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -7059,7 +6963,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="containsText" dxfId="176" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="167" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -7074,7 +6978,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26">
-    <cfRule type="containsText" dxfId="175" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="166" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -7089,7 +6993,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26">
-    <cfRule type="containsText" dxfId="174" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="165" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -7415,7 +7319,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="17" t="str">
         <f t="shared" si="0"/>
@@ -8367,7 +8271,7 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="J3:N20">
-    <cfRule type="containsText" dxfId="173" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="164" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="52">
@@ -8382,7 +8286,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J21:N24">
-    <cfRule type="containsText" dxfId="172" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="163" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="42">
@@ -8396,8 +8300,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J25 N25">
-    <cfRule type="containsText" dxfId="171" priority="15" operator="containsText" text="*-">
+  <conditionalFormatting sqref="N25 J25">
+    <cfRule type="containsText" dxfId="162" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
@@ -8412,7 +8316,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="containsText" dxfId="170" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="161" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="14">
@@ -8427,7 +8331,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L25">
-    <cfRule type="containsText" dxfId="169" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="160" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="12">
@@ -8442,7 +8346,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25">
-    <cfRule type="containsText" dxfId="168" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="159" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="10">
@@ -8456,8 +8360,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J26 N26">
-    <cfRule type="containsText" dxfId="167" priority="7" operator="containsText" text="*-">
+  <conditionalFormatting sqref="N26 J26">
+    <cfRule type="containsText" dxfId="158" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -8472,7 +8376,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="containsText" dxfId="166" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="157" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -8487,7 +8391,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26">
-    <cfRule type="containsText" dxfId="165" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="156" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -8502,7 +8406,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26">
-    <cfRule type="containsText" dxfId="164" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="155" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -9719,7 +9623,7 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="J3:J20 K3:M3 N3:N20">
-    <cfRule type="containsText" dxfId="163" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="154" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="56">
@@ -9734,7 +9638,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K20">
-    <cfRule type="containsText" dxfId="162" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="153" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="54">
@@ -9749,7 +9653,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="containsText" dxfId="161" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="152" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="52">
@@ -9764,7 +9668,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L20">
-    <cfRule type="containsText" dxfId="160" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="151" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="50">
@@ -9779,7 +9683,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4">
-    <cfRule type="containsText" dxfId="159" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="150" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="48">
@@ -9794,7 +9698,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M20">
-    <cfRule type="containsText" dxfId="158" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="149" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="46">
@@ -9809,7 +9713,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
-    <cfRule type="containsText" dxfId="157" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="148" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="44">
@@ -9824,7 +9728,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N21:N24 J21:J24">
-    <cfRule type="containsText" dxfId="156" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="147" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="40">
@@ -9839,7 +9743,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:K24">
-    <cfRule type="containsText" dxfId="155" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="146" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="38">
@@ -9854,7 +9758,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L21:L24">
-    <cfRule type="containsText" dxfId="154" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="145" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="36">
@@ -9869,7 +9773,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M21:M24">
-    <cfRule type="containsText" dxfId="153" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="144" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="34">
@@ -9883,8 +9787,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N25 J25">
-    <cfRule type="containsText" dxfId="152" priority="31" operator="containsText" text="*-">
+  <conditionalFormatting sqref="J25 N25">
+    <cfRule type="containsText" dxfId="143" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="32">
@@ -9899,7 +9803,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="containsText" dxfId="151" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="142" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="30">
@@ -9914,7 +9818,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L25">
-    <cfRule type="containsText" dxfId="150" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="141" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
@@ -9929,7 +9833,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25">
-    <cfRule type="containsText" dxfId="149" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="140" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="26">
@@ -9943,8 +9847,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J26 N26">
-    <cfRule type="containsText" dxfId="144" priority="7" operator="containsText" text="*-">
+  <conditionalFormatting sqref="N26 J26">
+    <cfRule type="containsText" dxfId="139" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -9959,7 +9863,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="containsText" dxfId="143" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="138" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -9974,7 +9878,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26">
-    <cfRule type="containsText" dxfId="142" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="137" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -9989,7 +9893,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26">
-    <cfRule type="containsText" dxfId="141" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="136" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -11328,7 +11232,7 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="K3:K21 L5:N6 O5:O21 L3:O4">
-    <cfRule type="containsText" dxfId="140" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="135" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="42">
@@ -11343,7 +11247,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19:L21">
-    <cfRule type="containsText" dxfId="139" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="134" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L19))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="40">
@@ -11358,7 +11262,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:L18">
-    <cfRule type="containsText" dxfId="138" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="133" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="38">
@@ -11373,7 +11277,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19:M21">
-    <cfRule type="containsText" dxfId="137" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="132" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M19))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="36">
@@ -11388,7 +11292,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:M18">
-    <cfRule type="containsText" dxfId="136" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="131" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="34">
@@ -11403,7 +11307,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:N21">
-    <cfRule type="containsText" dxfId="135" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="130" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N19))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="30">
@@ -11418,7 +11322,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7:N18">
-    <cfRule type="containsText" dxfId="134" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="129" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
@@ -11433,7 +11337,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O22:O25 K22:K25">
-    <cfRule type="containsText" dxfId="133" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="128" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="24">
@@ -11448,7 +11352,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L22:L25">
-    <cfRule type="containsText" dxfId="132" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="127" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="22">
@@ -11463,7 +11367,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M22:M25">
-    <cfRule type="containsText" dxfId="131" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="126" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="20">
@@ -11478,7 +11382,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22:N25">
-    <cfRule type="containsText" dxfId="130" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="125" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="18">
@@ -11492,8 +11396,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K26 O26">
-    <cfRule type="containsText" dxfId="129" priority="15" operator="containsText" text="*-">
+  <conditionalFormatting sqref="O26 K26">
+    <cfRule type="containsText" dxfId="124" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
@@ -11508,7 +11412,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26">
-    <cfRule type="containsText" dxfId="128" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="123" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="14">
@@ -11523,7 +11427,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26">
-    <cfRule type="containsText" dxfId="127" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="122" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="12">
@@ -11538,7 +11442,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26">
-    <cfRule type="containsText" dxfId="126" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="121" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="10">
@@ -11552,8 +11456,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K27 O27">
-    <cfRule type="containsText" dxfId="125" priority="7" operator="containsText" text="*-">
+  <conditionalFormatting sqref="O27 K27">
+    <cfRule type="containsText" dxfId="120" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -11568,7 +11472,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27">
-    <cfRule type="containsText" dxfId="124" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="119" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -11583,7 +11487,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M27">
-    <cfRule type="containsText" dxfId="123" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="118" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -11598,7 +11502,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N27">
-    <cfRule type="containsText" dxfId="122" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="117" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -12982,7 +12886,7 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="J3:K8 L3:M4 N3:N8 N10:N21 J10:K21">
-    <cfRule type="containsText" dxfId="121" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="116" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="44">
@@ -12997,7 +12901,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L8 L10:L21">
-    <cfRule type="containsText" dxfId="120" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="115" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="40">
@@ -13012,7 +12916,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5">
-    <cfRule type="containsText" dxfId="119" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="114" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="38">
@@ -13027,7 +12931,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:M8 M10:M21">
-    <cfRule type="containsText" dxfId="118" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="113" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="36">
@@ -13042,7 +12946,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5">
-    <cfRule type="containsText" dxfId="117" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="112" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="34">
@@ -13057,7 +12961,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L9">
-    <cfRule type="containsText" dxfId="116" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="111" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L9))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="30">
@@ -13072,7 +12976,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M9">
-    <cfRule type="containsText" dxfId="115" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="110" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M9))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
@@ -13087,7 +12991,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N9">
-    <cfRule type="containsText" dxfId="114" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="109" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N9))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="26">
@@ -13102,7 +13006,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9">
-    <cfRule type="containsText" dxfId="113" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="108" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K9))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="24">
@@ -13117,7 +13021,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9">
-    <cfRule type="containsText" dxfId="112" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="107" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J9))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="22">
@@ -13132,7 +13036,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J22:K25 N22:N25">
-    <cfRule type="containsText" dxfId="111" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="106" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="20">
@@ -13147,7 +13051,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L22:L25">
-    <cfRule type="containsText" dxfId="110" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="105" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="18">
@@ -13162,7 +13066,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M22:M25">
-    <cfRule type="containsText" dxfId="109" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="104" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
@@ -13177,7 +13081,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J26:K26 N26">
-    <cfRule type="containsText" dxfId="22" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="103" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="14">
@@ -13192,7 +13096,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26">
-    <cfRule type="containsText" dxfId="21" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="102" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="12">
@@ -13207,7 +13111,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26">
-    <cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="101" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="10">
@@ -13221,8 +13125,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J27 N27">
-    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="*-">
+  <conditionalFormatting sqref="N27 J27">
+    <cfRule type="containsText" dxfId="100" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -13237,7 +13141,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="99" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -13252,7 +13156,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27">
-    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="98" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -13267,7 +13171,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M27">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="97" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -14584,7 +14488,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="J3:J20 K3:K4 L3:M3 N3:N20">
-    <cfRule type="containsText" dxfId="108" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="96" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="38">
@@ -14599,7 +14503,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K20">
-    <cfRule type="containsText" dxfId="107" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="95" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="34">
@@ -14614,7 +14518,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5">
-    <cfRule type="containsText" dxfId="106" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="94" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="32">
@@ -14629,7 +14533,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4">
-    <cfRule type="containsText" dxfId="105" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="93" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="30">
@@ -14644,7 +14548,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L20">
-    <cfRule type="containsText" dxfId="104" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="92" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
@@ -14659,7 +14563,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
-    <cfRule type="containsText" dxfId="103" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="91" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="24">
@@ -14674,7 +14578,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5">
-    <cfRule type="containsText" dxfId="102" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="90" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="22">
@@ -14689,7 +14593,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:M20">
-    <cfRule type="containsText" dxfId="101" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="89" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="20">
@@ -14704,7 +14608,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N21:N22 J21:J22">
-    <cfRule type="containsText" dxfId="100" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="88" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
@@ -14719,7 +14623,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:K22">
-    <cfRule type="containsText" dxfId="99" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="87" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="14">
@@ -14734,7 +14638,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L21:L22">
-    <cfRule type="containsText" dxfId="98" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="86" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="12">
@@ -14749,7 +14653,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M21:M22">
-    <cfRule type="containsText" dxfId="97" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="85" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="10">
@@ -14764,7 +14668,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23:J24 L23:L24 N23:N24">
-    <cfRule type="containsText" dxfId="96" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="84" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -14779,7 +14683,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23:K24 M23:M24">
-    <cfRule type="containsText" dxfId="95" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="83" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -14794,7 +14698,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J25:J26 L25:L26 N25:N26">
-    <cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="82" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -14809,7 +14713,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K26 M25:M26">
-    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="81" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -16201,7 +16105,7 @@
     <mergeCell ref="K1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="K3:O3 K5:K21 M4 O5:O21">
-    <cfRule type="containsText" dxfId="94" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="80" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="48">
@@ -16216,7 +16120,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6">
-    <cfRule type="containsText" dxfId="93" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="79" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="46">
@@ -16231,7 +16135,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:L21">
-    <cfRule type="containsText" dxfId="92" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="78" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="44">
@@ -16246,7 +16150,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5">
-    <cfRule type="containsText" dxfId="91" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="77" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="42">
@@ -16261,7 +16165,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6">
-    <cfRule type="containsText" dxfId="90" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="76" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="40">
@@ -16276,7 +16180,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5">
-    <cfRule type="containsText" dxfId="89" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="75" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="38">
@@ -16291,7 +16195,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:M21">
-    <cfRule type="containsText" dxfId="88" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="74" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="36">
@@ -16306,7 +16210,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5">
-    <cfRule type="containsText" dxfId="87" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="73" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="32">
@@ -16321,7 +16225,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6">
-    <cfRule type="containsText" dxfId="86" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="72" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="30">
@@ -16336,7 +16240,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7:N21">
-    <cfRule type="containsText" dxfId="85" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="71" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
@@ -16351,7 +16255,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="containsText" dxfId="84" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="70" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="24">
@@ -16366,7 +16270,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4">
-    <cfRule type="containsText" dxfId="83" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="69" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="22">
@@ -16381,7 +16285,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="containsText" dxfId="82" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="68" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="20">
@@ -16396,7 +16300,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4">
-    <cfRule type="containsText" dxfId="81" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="67" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(O4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="18">
@@ -16411,7 +16315,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O22:O25 K22:K25">
-    <cfRule type="containsText" dxfId="80" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="66" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
@@ -16426,7 +16330,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L22:L25">
-    <cfRule type="containsText" dxfId="79" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="65" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="14">
@@ -16441,7 +16345,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M22:M25">
-    <cfRule type="containsText" dxfId="78" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="64" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="12">
@@ -16456,7 +16360,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22:N25">
-    <cfRule type="containsText" dxfId="77" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="63" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="10">
@@ -16471,7 +16375,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O26:O27 K26:K27">
-    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="62" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -16486,7 +16390,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26:L27">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="61" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -16501,7 +16405,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26:M27">
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="60" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -16516,7 +16420,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26:N27">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="59" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -16742,7 +16646,7 @@
         <v>428</v>
       </c>
       <c r="J5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
         <v>0</v>
@@ -17896,7 +17800,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="J3:J20 K3:K5 L3:M4 N3:N5">
-    <cfRule type="containsText" dxfId="76" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="58" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="114">
@@ -17911,7 +17815,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K12 K9 K15 K17:K18 K20">
-    <cfRule type="containsText" dxfId="75" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="57" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K9))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="112">
@@ -17926,7 +17830,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6">
-    <cfRule type="containsText" dxfId="74" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="56" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="110">
@@ -17941,7 +17845,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="containsText" dxfId="73" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="55" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="108">
@@ -17956,7 +17860,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8">
-    <cfRule type="containsText" dxfId="72" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="54" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K8))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="106">
@@ -17971,7 +17875,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K10">
-    <cfRule type="containsText" dxfId="71" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="53" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K10))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="104">
@@ -17986,7 +17890,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="70" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="52" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="102">
@@ -18001,7 +17905,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="containsText" dxfId="69" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="51" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K14))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="100">
@@ -18016,7 +17920,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="68" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="50" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K16))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="98">
@@ -18031,7 +17935,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19">
-    <cfRule type="containsText" dxfId="67" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="49" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K19))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="96">
@@ -18046,7 +17950,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L11:L12 L9 L15 L17:L18 L20">
-    <cfRule type="containsText" dxfId="66" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="48" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L9))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="92">
@@ -18061,7 +17965,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6">
-    <cfRule type="containsText" dxfId="65" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="47" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="90">
@@ -18076,7 +17980,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7">
-    <cfRule type="containsText" dxfId="64" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="46" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="88">
@@ -18091,7 +17995,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L8">
-    <cfRule type="containsText" dxfId="63" priority="85" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="45" priority="85" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L8))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="86">
@@ -18106,7 +18010,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10">
-    <cfRule type="containsText" dxfId="62" priority="83" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="44" priority="83" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L10))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="84">
@@ -18121,7 +18025,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L13">
-    <cfRule type="containsText" dxfId="61" priority="81" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="43" priority="81" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L13))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="82">
@@ -18136,7 +18040,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14">
-    <cfRule type="containsText" dxfId="60" priority="79" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="42" priority="79" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L14))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="80">
@@ -18151,7 +18055,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L16">
-    <cfRule type="containsText" dxfId="59" priority="77" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="41" priority="77" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L16))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="78">
@@ -18166,7 +18070,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19">
-    <cfRule type="containsText" dxfId="58" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="40" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L19))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="76">
@@ -18181,7 +18085,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5">
-    <cfRule type="containsText" dxfId="57" priority="73" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="73" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="74">
@@ -18196,7 +18100,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12">
-    <cfRule type="containsText" dxfId="56" priority="71" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="38" priority="71" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M12))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="72">
@@ -18210,8 +18114,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M9 M11">
-    <cfRule type="containsText" dxfId="55" priority="69" operator="containsText" text="*-">
+  <conditionalFormatting sqref="M11 M9">
+    <cfRule type="containsText" dxfId="37" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M9))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="70">
@@ -18226,7 +18130,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6">
-    <cfRule type="containsText" dxfId="54" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="68">
@@ -18241,7 +18145,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7">
-    <cfRule type="containsText" dxfId="53" priority="65" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="65" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="66">
@@ -18256,7 +18160,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8">
-    <cfRule type="containsText" dxfId="52" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M8))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="64">
@@ -18271,7 +18175,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10">
-    <cfRule type="containsText" dxfId="51" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M10))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="62">
@@ -18286,7 +18190,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5">
-    <cfRule type="containsText" dxfId="50" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M5))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="60">
@@ -18301,7 +18205,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M17:M18 M15 M20">
-    <cfRule type="containsText" dxfId="49" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M15))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="58">
@@ -18316,7 +18220,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13">
-    <cfRule type="containsText" dxfId="48" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M13))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="56">
@@ -18331,7 +18235,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M14">
-    <cfRule type="containsText" dxfId="47" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M14))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="54">
@@ -18346,7 +18250,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M16">
-    <cfRule type="containsText" dxfId="46" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M16))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="52">
@@ -18361,7 +18265,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19">
-    <cfRule type="containsText" dxfId="45" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M19))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="50">
@@ -18376,7 +18280,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N9:N20">
-    <cfRule type="containsText" dxfId="44" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N9))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="48">
@@ -18391,7 +18295,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7">
-    <cfRule type="containsText" dxfId="43" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="25" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="46">
@@ -18406,7 +18310,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8">
-    <cfRule type="containsText" dxfId="42" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N8))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="44">
@@ -18421,7 +18325,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6">
-    <cfRule type="containsText" dxfId="41" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="42">
@@ -18436,7 +18340,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J21:J22 J24">
-    <cfRule type="containsText" dxfId="40" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="40">
@@ -18451,7 +18355,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:K22 K24">
-    <cfRule type="containsText" dxfId="39" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="38">
@@ -18466,7 +18370,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L21:L22 L24">
-    <cfRule type="containsText" dxfId="38" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="36">
@@ -18481,7 +18385,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M21:M22 M24">
-    <cfRule type="containsText" dxfId="37" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="34">
@@ -18496,7 +18400,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N21:N22 N24">
-    <cfRule type="containsText" dxfId="36" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="32">
@@ -18511,7 +18415,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23">
-    <cfRule type="containsText" dxfId="35" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="30">
@@ -18526,7 +18430,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23">
-    <cfRule type="containsText" dxfId="34" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
@@ -18541,7 +18445,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23">
-    <cfRule type="containsText" dxfId="33" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="26">
@@ -18556,7 +18460,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23">
-    <cfRule type="containsText" dxfId="32" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="24">
@@ -18571,7 +18475,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="containsText" dxfId="31" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="22">
@@ -18586,7 +18490,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J25">
-    <cfRule type="containsText" dxfId="9" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="20">
@@ -18601,7 +18505,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="containsText" dxfId="8" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="18">
@@ -18616,7 +18520,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L25">
-    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
@@ -18631,7 +18535,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25">
-    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="14">
@@ -18646,7 +18550,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="12">
@@ -18661,7 +18565,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J26">
-    <cfRule type="containsText" dxfId="4" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="10">
@@ -18676,7 +18580,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -18691,7 +18595,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L26">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(L26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -18706,7 +18610,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -18721,7 +18625,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">

--- a/Collections/EURO/Germany/#EURO#Germany#Regular#[2002-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Germany/#EURO#Germany#Regular#[2002-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Germany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B8BC26-F9F8-4666-B319-E32868E9AD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6330DAA-C2AB-45D7-BD87-6F12F48D2ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -5593,7 +5593,7 @@
         <v>66</v>
       </c>
       <c r="J5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
         <v>0</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="17" t="str">
         <f t="shared" si="0"/>
@@ -6827,7 +6827,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J23 N23">
+  <conditionalFormatting sqref="N23 J23">
     <cfRule type="containsText" dxfId="176" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J23))))</formula>
     </cfRule>
@@ -6887,7 +6887,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N25 J25">
+  <conditionalFormatting sqref="J25 N25">
     <cfRule type="containsText" dxfId="172" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
     </cfRule>
@@ -6947,7 +6947,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N26 J26">
+  <conditionalFormatting sqref="J26 N26">
     <cfRule type="containsText" dxfId="168" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J26))))</formula>
     </cfRule>
@@ -7130,7 +7130,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="1">
         <v>0</v>
@@ -7313,7 +7313,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
@@ -8300,7 +8300,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N25 J25">
+  <conditionalFormatting sqref="J25 N25">
     <cfRule type="containsText" dxfId="162" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
     </cfRule>
@@ -8360,7 +8360,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N26 J26">
+  <conditionalFormatting sqref="J26 N26">
     <cfRule type="containsText" dxfId="158" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J26))))</formula>
     </cfRule>
@@ -8534,7 +8534,7 @@
         <v>187</v>
       </c>
       <c r="J3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
         <v>0</v>
@@ -8546,11 +8546,11 @@
         <v>0</v>
       </c>
       <c r="N3" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" s="17" t="str">
         <f t="shared" ref="O3:O20" si="0">IF(OR(AND(J3&gt;1,J3&lt;&gt;"-"),AND(K3&gt;1,K3&lt;&gt;"-"),AND(L3&gt;1,L3&lt;&gt;"-"),AND(M3&gt;1,M3&lt;&gt;"-"),AND(N3&gt;1,N3&lt;&gt;"-")),"Can exchange","")</f>
-        <v/>
+        <v>Can exchange</v>
       </c>
       <c r="Q3" s="4"/>
     </row>
@@ -8778,7 +8778,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="17" t="str">
         <f t="shared" si="0"/>
@@ -8910,7 +8910,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
@@ -9787,7 +9787,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J25 N25">
+  <conditionalFormatting sqref="N25 J25">
     <cfRule type="containsText" dxfId="143" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
     </cfRule>
@@ -9847,7 +9847,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N26 J26">
+  <conditionalFormatting sqref="J26 N26">
     <cfRule type="containsText" dxfId="139" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J26))))</formula>
     </cfRule>
@@ -11396,7 +11396,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O26 K26">
+  <conditionalFormatting sqref="K26 O26">
     <cfRule type="containsText" dxfId="124" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K26))))</formula>
     </cfRule>
@@ -11456,7 +11456,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O27 K27">
+  <conditionalFormatting sqref="K27 O27">
     <cfRule type="containsText" dxfId="120" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K27))))</formula>
     </cfRule>
@@ -11832,7 +11832,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="23">
         <v>0</v>
@@ -13125,7 +13125,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N27 J27">
+  <conditionalFormatting sqref="J27 N27">
     <cfRule type="containsText" dxfId="100" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J27))))</formula>
     </cfRule>
@@ -18114,7 +18114,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M11 M9">
+  <conditionalFormatting sqref="M9 M11">
     <cfRule type="containsText" dxfId="37" priority="69" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(M9))))</formula>
     </cfRule>
